--- a/Config/Datas/container_stack.xlsx
+++ b/Config/Datas/container_stack.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="container_item_stack_override" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="container_stack_tag_rule" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="container_item_stack_override" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="container_stack_tag_rule" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -688,7 +688,6 @@
       <c r="D5" t="n">
         <v>0</v>
       </c>
-      <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
         <v>1</v>
       </c>
@@ -727,7 +726,6 @@
       <c r="D8" t="n">
         <v>0</v>
       </c>
-      <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
         <v>1</v>
       </c>
@@ -744,7 +742,6 @@
       <c r="D9" t="n">
         <v>0</v>
       </c>
-      <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
         <v>1</v>
       </c>
@@ -761,7 +758,6 @@
       <c r="D10" t="n">
         <v>0</v>
       </c>
-      <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
         <v>999</v>
       </c>
@@ -778,7 +774,6 @@
       <c r="D11" t="n">
         <v>0</v>
       </c>
-      <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
         <v>1</v>
       </c>
